--- a/docs/画面構想.xlsx
+++ b/docs/画面構想.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myProgram\GitHub\ForCustomers\body_inspect_visualize_coba\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD47C71-6BCC-4FDF-82FA-C26E282B8BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC9AC8A-FC71-4DE8-A6D8-64405BA10480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1125" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="126">
   <si>
     <t>シフト:</t>
     <phoneticPr fontId="2"/>
@@ -326,13 +326,6 @@
   </si>
   <si>
     <t>自動入力※6</t>
-    <rPh sb="0" eb="4">
-      <t>ジドウニュウリョク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>自動入力※7</t>
     <rPh sb="0" eb="4">
       <t>ジドウニュウリョク</t>
     </rPh>
@@ -3485,7 +3478,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
-            <a:t>：「異常」選択時にメッセージ表示「製品以上の打ち上げを実施しましたか？」（ポカヨケとしてデフォルトなし）</a:t>
+            <a:t>：「異常」選択時にメッセージ表示「製品異常の打ち上げを実施しましたか？」（ポカヨケとしてデフォルトなし）</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
         </a:p>
@@ -3566,7 +3559,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
-            <a:t>：バーコード入力</a:t>
+            <a:t>：</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
         </a:p>
@@ -5052,15 +5045,15 @@
     </row>
     <row r="5" spans="2:18">
       <c r="B5" s="55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C5" s="55"/>
       <c r="D5" s="55" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="55"/>
       <c r="F5" s="55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G5" s="55" t="s">
         <v>4</v>
@@ -5159,11 +5152,11 @@
     </row>
     <row r="9" spans="2:18">
       <c r="B9" s="55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="55" t="s">
@@ -5171,10 +5164,10 @@
       </c>
       <c r="G9" s="55"/>
       <c r="H9" s="55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J9" s="55" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="L9" s="55" t="s">
         <v>3</v>
@@ -5188,15 +5181,15 @@
         <v>34</v>
       </c>
       <c r="R9" s="55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="2:18">
       <c r="B11" s="49" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:18">
@@ -5204,7 +5197,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E12" s="57"/>
       <c r="F12" s="57"/>
@@ -5243,15 +5236,15 @@
   <sheetData>
     <row r="2" spans="2:10">
       <c r="B2" s="54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="62" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="62" t="s">
         <v>45</v>
-      </c>
-      <c r="C3" s="62" t="s">
-        <v>46</v>
       </c>
       <c r="D3" s="60"/>
       <c r="E3" s="60"/>
@@ -5286,7 +5279,7 @@
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="60" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="60"/>
@@ -5298,28 +5291,28 @@
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="62" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="62" t="s">
+      <c r="D7" s="62" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="62" t="s">
+      <c r="E7" s="62" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E7" s="62" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="62" t="s">
+      <c r="G7" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="62" t="s">
+      <c r="H7" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="I7" s="62" t="s">
         <v>42</v>
-      </c>
-      <c r="I7" s="62" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="8" spans="2:10">
@@ -5386,7 +5379,7 @@
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -5398,31 +5391,31 @@
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="62" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="D12" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="62" t="s">
+      <c r="E12" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="62" t="s">
+      <c r="F12" s="62" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="62" t="s">
+      <c r="G12" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="G12" s="62" t="s">
+      <c r="H12" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="I12" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="I12" s="62" t="s">
+      <c r="J12" s="62" t="s">
         <v>57</v>
-      </c>
-      <c r="J12" s="62" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="13" spans="2:10">
@@ -5531,7 +5524,7 @@
   <sheetData>
     <row r="1" spans="1:93" ht="13.5" customHeight="1">
       <c r="A1" s="240" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="241"/>
       <c r="C1" s="241"/>
@@ -5725,7 +5718,7 @@
     </row>
     <row r="4" spans="1:93" ht="13.5" customHeight="1">
       <c r="A4" s="246" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" s="247"/>
       <c r="C4" s="247"/>
@@ -5737,7 +5730,7 @@
       <c r="I4" s="247"/>
       <c r="J4" s="247"/>
       <c r="K4" s="250" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L4" s="250"/>
       <c r="M4" s="250"/>
@@ -5763,22 +5756,22 @@
     </row>
     <row r="6" spans="1:93" ht="13.5" customHeight="1" thickTop="1">
       <c r="A6" s="173" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" s="65"/>
       <c r="C6" s="174"/>
       <c r="D6" s="175" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E6" s="65"/>
       <c r="F6" s="68"/>
       <c r="G6" s="148" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H6" s="65"/>
       <c r="I6" s="68"/>
       <c r="J6" s="148" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K6" s="65"/>
       <c r="L6" s="65"/>
@@ -5790,35 +5783,35 @@
       <c r="R6" s="65"/>
       <c r="S6" s="174"/>
       <c r="T6" s="256" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U6" s="257"/>
       <c r="V6" s="175" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W6" s="65"/>
       <c r="X6" s="65"/>
       <c r="Y6" s="65"/>
       <c r="Z6" s="174"/>
       <c r="AA6" s="175" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB6" s="65"/>
       <c r="AC6" s="65"/>
       <c r="AD6" s="65"/>
       <c r="AE6" s="68"/>
       <c r="AF6" s="148" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AG6" s="65"/>
       <c r="AH6" s="224"/>
       <c r="AI6" s="226" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AJ6" s="227"/>
       <c r="AK6" s="228"/>
       <c r="AL6" s="232" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AM6" s="233"/>
       <c r="AN6" s="233"/>
@@ -5839,7 +5832,7 @@
       <c r="BC6" s="233"/>
       <c r="BD6" s="234"/>
       <c r="BE6" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="BF6" s="65"/>
       <c r="BG6" s="65"/>
@@ -5848,7 +5841,7 @@
       <c r="BJ6" s="65"/>
       <c r="BK6" s="68"/>
       <c r="BL6" s="239" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="BM6" s="65"/>
       <c r="BN6" s="65"/>
@@ -5858,43 +5851,43 @@
       <c r="BR6" s="65"/>
       <c r="BS6" s="68"/>
       <c r="BT6" s="148" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="BU6" s="65"/>
       <c r="BV6" s="68"/>
       <c r="BW6" s="201" t="s">
+        <v>78</v>
+      </c>
+      <c r="BX6" s="201" t="s">
         <v>79</v>
       </c>
-      <c r="BX6" s="201" t="s">
+      <c r="BY6" s="148" t="s">
         <v>80</v>
-      </c>
-      <c r="BY6" s="148" t="s">
-        <v>81</v>
       </c>
       <c r="BZ6" s="65"/>
       <c r="CA6" s="149"/>
       <c r="CB6" s="206" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="CC6" s="207"/>
       <c r="CD6" s="212" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="CE6" s="213"/>
       <c r="CF6" s="218" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="CG6" s="219"/>
       <c r="CH6" s="178" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="CI6" s="179"/>
       <c r="CJ6" s="178" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="CK6" s="184"/>
       <c r="CL6" s="187" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="CM6" s="188"/>
       <c r="CN6" s="189"/>
@@ -5904,7 +5897,7 @@
       <c r="B7" s="197"/>
       <c r="C7" s="255"/>
       <c r="D7" s="196" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E7" s="197"/>
       <c r="F7" s="198"/>
@@ -6001,7 +5994,7 @@
       <c r="B8" s="67"/>
       <c r="C8" s="114"/>
       <c r="D8" s="116" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E8" s="67"/>
       <c r="F8" s="69"/>
@@ -6021,63 +6014,63 @@
       <c r="T8" s="260"/>
       <c r="U8" s="261"/>
       <c r="V8" s="116" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="W8" s="67"/>
       <c r="X8" s="67"/>
       <c r="Y8" s="67"/>
       <c r="Z8" s="114"/>
       <c r="AA8" s="116" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AB8" s="67"/>
       <c r="AC8" s="67"/>
       <c r="AD8" s="67"/>
       <c r="AE8" s="69"/>
       <c r="AF8" s="77" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AG8" s="67"/>
       <c r="AH8" s="199"/>
       <c r="AI8" s="66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AJ8" s="67"/>
       <c r="AK8" s="69"/>
       <c r="AL8" s="200" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AM8" s="166"/>
       <c r="AN8" s="165" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AO8" s="166"/>
       <c r="AP8" s="165" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AQ8" s="166"/>
       <c r="AR8" s="176" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AS8" s="177"/>
       <c r="AT8" s="165" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AU8" s="166"/>
       <c r="AV8" s="165" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AW8" s="166"/>
       <c r="AX8" s="165" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AY8" s="167"/>
       <c r="AZ8" s="167" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="BA8" s="168"/>
       <c r="BB8" s="169" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="BC8" s="170"/>
       <c r="BD8" s="171"/>
@@ -6102,7 +6095,7 @@
       <c r="BW8" s="203"/>
       <c r="BX8" s="203"/>
       <c r="BY8" s="77" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="BZ8" s="67"/>
       <c r="CA8" s="172"/>
@@ -6122,12 +6115,12 @@
     </row>
     <row r="9" spans="1:93" ht="15" customHeight="1">
       <c r="A9" s="173" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B9" s="65"/>
       <c r="C9" s="174"/>
       <c r="D9" s="175" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E9" s="65"/>
       <c r="F9" s="68"/>
@@ -6136,11 +6129,11 @@
       <c r="I9" s="6"/>
       <c r="J9" s="9"/>
       <c r="M9" s="65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N9" s="65"/>
       <c r="P9" s="65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q9" s="65"/>
       <c r="R9" s="6"/>
@@ -6148,26 +6141,26 @@
       <c r="T9" s="175"/>
       <c r="U9" s="174"/>
       <c r="V9" s="155" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W9" s="156"/>
       <c r="X9" s="156"/>
       <c r="Y9" s="156"/>
       <c r="Z9" s="157"/>
       <c r="AA9" s="155" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB9" s="156"/>
       <c r="AC9" s="156"/>
       <c r="AD9" s="156"/>
       <c r="AE9" s="158"/>
       <c r="AF9" s="159" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG9" s="160"/>
       <c r="AH9" s="161"/>
       <c r="AI9" s="162" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ9" s="160"/>
       <c r="AK9" s="163"/>
@@ -6191,41 +6184,41 @@
       <c r="BC9" s="151"/>
       <c r="BD9" s="152"/>
       <c r="BE9" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF9" s="65"/>
       <c r="BG9" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH9" s="68"/>
       <c r="BI9" s="148" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ9" s="65"/>
       <c r="BK9" s="65"/>
       <c r="BL9" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM9" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="BM9" s="12" t="s">
+      <c r="BN9" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="BN9" s="12" t="s">
+      <c r="BO9" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="BO9" s="12" t="s">
+      <c r="BP9" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="BP9" s="12" t="s">
+      <c r="BQ9" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="BQ9" s="12" t="s">
+      <c r="BR9" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="BR9" s="12" t="s">
+      <c r="BS9" s="13" t="s">
         <v>118</v>
-      </c>
-      <c r="BS9" s="13" t="s">
-        <v>119</v>
       </c>
       <c r="BT9" s="65"/>
       <c r="BU9" s="65"/>
@@ -6307,7 +6300,7 @@
       <c r="BG10" s="120"/>
       <c r="BH10" s="121"/>
       <c r="BI10" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ10" s="120"/>
       <c r="BK10" s="120"/>
@@ -6343,12 +6336,12 @@
     </row>
     <row r="11" spans="1:93" ht="15" customHeight="1">
       <c r="A11" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B11" s="71"/>
       <c r="C11" s="112"/>
       <c r="D11" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E11" s="71"/>
       <c r="F11" s="72"/>
@@ -6359,12 +6352,12 @@
       <c r="K11" s="31"/>
       <c r="L11" s="31"/>
       <c r="M11" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N11" s="71"/>
       <c r="O11" s="31"/>
       <c r="P11" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q11" s="71"/>
       <c r="R11" s="29"/>
@@ -6372,26 +6365,26 @@
       <c r="T11" s="115"/>
       <c r="U11" s="112"/>
       <c r="V11" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W11" s="93"/>
       <c r="X11" s="93"/>
       <c r="Y11" s="93"/>
       <c r="Z11" s="117"/>
       <c r="AA11" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB11" s="93"/>
       <c r="AC11" s="93"/>
       <c r="AD11" s="93"/>
       <c r="AE11" s="94"/>
       <c r="AF11" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG11" s="99"/>
       <c r="AH11" s="100"/>
       <c r="AI11" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ11" s="99"/>
       <c r="AK11" s="105"/>
@@ -6415,41 +6408,41 @@
       <c r="BC11" s="87"/>
       <c r="BD11" s="88"/>
       <c r="BE11" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF11" s="65"/>
       <c r="BG11" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH11" s="68"/>
       <c r="BI11" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ11" s="71"/>
       <c r="BK11" s="71"/>
       <c r="BL11" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="BM11" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="BM11" s="23" t="s">
+      <c r="BN11" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN11" s="23" t="s">
+      <c r="BO11" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO11" s="23" t="s">
+      <c r="BP11" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP11" s="23" t="s">
+      <c r="BQ11" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ11" s="23" t="s">
+      <c r="BR11" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR11" s="23" t="s">
+      <c r="BS11" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS11" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT11" s="71"/>
       <c r="BU11" s="71"/>
@@ -6535,7 +6528,7 @@
       <c r="BG12" s="120"/>
       <c r="BH12" s="121"/>
       <c r="BI12" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ12" s="120"/>
       <c r="BK12" s="120"/>
@@ -6571,12 +6564,12 @@
     </row>
     <row r="13" spans="1:93" ht="15" customHeight="1">
       <c r="A13" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B13" s="71"/>
       <c r="C13" s="112"/>
       <c r="D13" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E13" s="71"/>
       <c r="F13" s="72"/>
@@ -6587,12 +6580,12 @@
       <c r="K13" s="31"/>
       <c r="L13" s="31"/>
       <c r="M13" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N13" s="71"/>
       <c r="O13" s="31"/>
       <c r="P13" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q13" s="71"/>
       <c r="R13" s="29"/>
@@ -6600,26 +6593,26 @@
       <c r="T13" s="115"/>
       <c r="U13" s="112"/>
       <c r="V13" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W13" s="93"/>
       <c r="X13" s="93"/>
       <c r="Y13" s="93"/>
       <c r="Z13" s="117"/>
       <c r="AA13" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB13" s="93"/>
       <c r="AC13" s="93"/>
       <c r="AD13" s="93"/>
       <c r="AE13" s="94"/>
       <c r="AF13" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG13" s="99"/>
       <c r="AH13" s="100"/>
       <c r="AI13" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ13" s="99"/>
       <c r="AK13" s="105"/>
@@ -6643,41 +6636,41 @@
       <c r="BC13" s="145"/>
       <c r="BD13" s="146"/>
       <c r="BE13" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF13" s="65"/>
       <c r="BG13" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH13" s="68"/>
       <c r="BI13" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ13" s="71"/>
       <c r="BK13" s="71"/>
       <c r="BL13" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM13" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN13" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN13" s="23" t="s">
+      <c r="BO13" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO13" s="23" t="s">
+      <c r="BP13" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP13" s="23" t="s">
+      <c r="BQ13" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ13" s="23" t="s">
+      <c r="BR13" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR13" s="23" t="s">
+      <c r="BS13" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS13" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT13" s="71"/>
       <c r="BU13" s="71"/>
@@ -6763,7 +6756,7 @@
       <c r="BG14" s="120"/>
       <c r="BH14" s="121"/>
       <c r="BI14" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ14" s="120"/>
       <c r="BK14" s="120"/>
@@ -6799,12 +6792,12 @@
     </row>
     <row r="15" spans="1:93" ht="15" customHeight="1">
       <c r="A15" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B15" s="71"/>
       <c r="C15" s="112"/>
       <c r="D15" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E15" s="71"/>
       <c r="F15" s="72"/>
@@ -6815,12 +6808,12 @@
       <c r="K15" s="31"/>
       <c r="L15" s="31"/>
       <c r="M15" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N15" s="71"/>
       <c r="O15" s="31"/>
       <c r="P15" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="71"/>
       <c r="R15" s="29"/>
@@ -6828,26 +6821,26 @@
       <c r="T15" s="115"/>
       <c r="U15" s="112"/>
       <c r="V15" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W15" s="93"/>
       <c r="X15" s="93"/>
       <c r="Y15" s="93"/>
       <c r="Z15" s="117"/>
       <c r="AA15" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB15" s="93"/>
       <c r="AC15" s="93"/>
       <c r="AD15" s="93"/>
       <c r="AE15" s="94"/>
       <c r="AF15" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG15" s="99"/>
       <c r="AH15" s="100"/>
       <c r="AI15" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ15" s="99"/>
       <c r="AK15" s="105"/>
@@ -6871,41 +6864,41 @@
       <c r="BC15" s="87"/>
       <c r="BD15" s="88"/>
       <c r="BE15" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF15" s="65"/>
       <c r="BG15" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH15" s="68"/>
       <c r="BI15" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ15" s="71"/>
       <c r="BK15" s="71"/>
       <c r="BL15" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM15" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN15" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN15" s="23" t="s">
+      <c r="BO15" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO15" s="23" t="s">
+      <c r="BP15" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP15" s="23" t="s">
+      <c r="BQ15" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ15" s="23" t="s">
+      <c r="BR15" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR15" s="23" t="s">
+      <c r="BS15" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS15" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT15" s="71"/>
       <c r="BU15" s="71"/>
@@ -6991,7 +6984,7 @@
       <c r="BG16" s="120"/>
       <c r="BH16" s="121"/>
       <c r="BI16" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ16" s="120"/>
       <c r="BK16" s="120"/>
@@ -7027,12 +7020,12 @@
     </row>
     <row r="17" spans="1:92" ht="15" customHeight="1">
       <c r="A17" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B17" s="71"/>
       <c r="C17" s="112"/>
       <c r="D17" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" s="71"/>
       <c r="F17" s="72"/>
@@ -7043,12 +7036,12 @@
       <c r="K17" s="31"/>
       <c r="L17" s="31"/>
       <c r="M17" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N17" s="71"/>
       <c r="O17" s="31"/>
       <c r="P17" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q17" s="71"/>
       <c r="R17" s="29"/>
@@ -7056,26 +7049,26 @@
       <c r="T17" s="115"/>
       <c r="U17" s="112"/>
       <c r="V17" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W17" s="93"/>
       <c r="X17" s="93"/>
       <c r="Y17" s="93"/>
       <c r="Z17" s="117"/>
       <c r="AA17" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB17" s="93"/>
       <c r="AC17" s="93"/>
       <c r="AD17" s="93"/>
       <c r="AE17" s="94"/>
       <c r="AF17" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG17" s="99"/>
       <c r="AH17" s="100"/>
       <c r="AI17" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ17" s="99"/>
       <c r="AK17" s="105"/>
@@ -7099,41 +7092,41 @@
       <c r="BC17" s="87"/>
       <c r="BD17" s="88"/>
       <c r="BE17" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF17" s="65"/>
       <c r="BG17" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH17" s="68"/>
       <c r="BI17" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ17" s="71"/>
       <c r="BK17" s="71"/>
       <c r="BL17" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM17" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN17" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN17" s="23" t="s">
+      <c r="BO17" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO17" s="23" t="s">
+      <c r="BP17" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP17" s="23" t="s">
+      <c r="BQ17" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ17" s="23" t="s">
+      <c r="BR17" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR17" s="23" t="s">
+      <c r="BS17" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS17" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT17" s="71"/>
       <c r="BU17" s="71"/>
@@ -7219,7 +7212,7 @@
       <c r="BG18" s="120"/>
       <c r="BH18" s="121"/>
       <c r="BI18" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ18" s="120"/>
       <c r="BK18" s="120"/>
@@ -7255,12 +7248,12 @@
     </row>
     <row r="19" spans="1:92" ht="15" customHeight="1">
       <c r="A19" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B19" s="71"/>
       <c r="C19" s="112"/>
       <c r="D19" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="71"/>
       <c r="F19" s="72"/>
@@ -7271,12 +7264,12 @@
       <c r="K19" s="31"/>
       <c r="L19" s="31"/>
       <c r="M19" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N19" s="71"/>
       <c r="O19" s="31"/>
       <c r="P19" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q19" s="71"/>
       <c r="R19" s="29"/>
@@ -7284,26 +7277,26 @@
       <c r="T19" s="115"/>
       <c r="U19" s="112"/>
       <c r="V19" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W19" s="93"/>
       <c r="X19" s="93"/>
       <c r="Y19" s="93"/>
       <c r="Z19" s="117"/>
       <c r="AA19" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB19" s="93"/>
       <c r="AC19" s="93"/>
       <c r="AD19" s="93"/>
       <c r="AE19" s="94"/>
       <c r="AF19" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG19" s="99"/>
       <c r="AH19" s="100"/>
       <c r="AI19" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ19" s="99"/>
       <c r="AK19" s="105"/>
@@ -7327,41 +7320,41 @@
       <c r="BC19" s="87"/>
       <c r="BD19" s="88"/>
       <c r="BE19" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF19" s="65"/>
       <c r="BG19" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH19" s="68"/>
       <c r="BI19" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ19" s="71"/>
       <c r="BK19" s="71"/>
       <c r="BL19" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM19" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN19" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN19" s="23" t="s">
+      <c r="BO19" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO19" s="23" t="s">
+      <c r="BP19" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP19" s="23" t="s">
+      <c r="BQ19" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ19" s="23" t="s">
+      <c r="BR19" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR19" s="23" t="s">
+      <c r="BS19" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS19" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT19" s="71"/>
       <c r="BU19" s="71"/>
@@ -7447,7 +7440,7 @@
       <c r="BG20" s="120"/>
       <c r="BH20" s="121"/>
       <c r="BI20" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ20" s="120"/>
       <c r="BK20" s="120"/>
@@ -7483,12 +7476,12 @@
     </row>
     <row r="21" spans="1:92" ht="15" customHeight="1">
       <c r="A21" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B21" s="71"/>
       <c r="C21" s="112"/>
       <c r="D21" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E21" s="71"/>
       <c r="F21" s="72"/>
@@ -7499,12 +7492,12 @@
       <c r="K21" s="31"/>
       <c r="L21" s="31"/>
       <c r="M21" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N21" s="71"/>
       <c r="O21" s="31"/>
       <c r="P21" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q21" s="71"/>
       <c r="R21" s="29"/>
@@ -7512,26 +7505,26 @@
       <c r="T21" s="115"/>
       <c r="U21" s="112"/>
       <c r="V21" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W21" s="93"/>
       <c r="X21" s="93"/>
       <c r="Y21" s="93"/>
       <c r="Z21" s="117"/>
       <c r="AA21" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB21" s="93"/>
       <c r="AC21" s="93"/>
       <c r="AD21" s="93"/>
       <c r="AE21" s="94"/>
       <c r="AF21" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG21" s="99"/>
       <c r="AH21" s="100"/>
       <c r="AI21" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ21" s="99"/>
       <c r="AK21" s="105"/>
@@ -7555,41 +7548,41 @@
       <c r="BC21" s="87"/>
       <c r="BD21" s="88"/>
       <c r="BE21" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF21" s="65"/>
       <c r="BG21" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH21" s="68"/>
       <c r="BI21" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ21" s="71"/>
       <c r="BK21" s="71"/>
       <c r="BL21" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM21" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN21" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN21" s="23" t="s">
+      <c r="BO21" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO21" s="23" t="s">
+      <c r="BP21" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP21" s="23" t="s">
+      <c r="BQ21" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ21" s="23" t="s">
+      <c r="BR21" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR21" s="23" t="s">
+      <c r="BS21" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS21" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT21" s="71"/>
       <c r="BU21" s="71"/>
@@ -7675,7 +7668,7 @@
       <c r="BG22" s="120"/>
       <c r="BH22" s="121"/>
       <c r="BI22" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ22" s="120"/>
       <c r="BK22" s="120"/>
@@ -7711,12 +7704,12 @@
     </row>
     <row r="23" spans="1:92" ht="15" customHeight="1">
       <c r="A23" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" s="71"/>
       <c r="C23" s="112"/>
       <c r="D23" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E23" s="71"/>
       <c r="F23" s="72"/>
@@ -7727,12 +7720,12 @@
       <c r="K23" s="31"/>
       <c r="L23" s="31"/>
       <c r="M23" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N23" s="71"/>
       <c r="O23" s="31"/>
       <c r="P23" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q23" s="71"/>
       <c r="R23" s="29"/>
@@ -7740,26 +7733,26 @@
       <c r="T23" s="115"/>
       <c r="U23" s="112"/>
       <c r="V23" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W23" s="93"/>
       <c r="X23" s="93"/>
       <c r="Y23" s="93"/>
       <c r="Z23" s="117"/>
       <c r="AA23" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB23" s="93"/>
       <c r="AC23" s="93"/>
       <c r="AD23" s="93"/>
       <c r="AE23" s="94"/>
       <c r="AF23" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG23" s="99"/>
       <c r="AH23" s="100"/>
       <c r="AI23" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ23" s="99"/>
       <c r="AK23" s="105"/>
@@ -7783,41 +7776,41 @@
       <c r="BC23" s="87"/>
       <c r="BD23" s="88"/>
       <c r="BE23" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF23" s="65"/>
       <c r="BG23" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH23" s="68"/>
       <c r="BI23" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ23" s="71"/>
       <c r="BK23" s="71"/>
       <c r="BL23" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM23" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN23" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN23" s="23" t="s">
+      <c r="BO23" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO23" s="23" t="s">
+      <c r="BP23" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP23" s="23" t="s">
+      <c r="BQ23" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ23" s="23" t="s">
+      <c r="BR23" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR23" s="23" t="s">
+      <c r="BS23" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS23" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT23" s="71"/>
       <c r="BU23" s="71"/>
@@ -7903,7 +7896,7 @@
       <c r="BG24" s="120"/>
       <c r="BH24" s="121"/>
       <c r="BI24" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ24" s="120"/>
       <c r="BK24" s="120"/>
@@ -7939,12 +7932,12 @@
     </row>
     <row r="25" spans="1:92" ht="15" customHeight="1">
       <c r="A25" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" s="71"/>
       <c r="C25" s="112"/>
       <c r="D25" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E25" s="71"/>
       <c r="F25" s="72"/>
@@ -7955,12 +7948,12 @@
       <c r="K25" s="31"/>
       <c r="L25" s="31"/>
       <c r="M25" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N25" s="71"/>
       <c r="O25" s="31"/>
       <c r="P25" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q25" s="71"/>
       <c r="R25" s="29"/>
@@ -7968,26 +7961,26 @@
       <c r="T25" s="115"/>
       <c r="U25" s="112"/>
       <c r="V25" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W25" s="93"/>
       <c r="X25" s="93"/>
       <c r="Y25" s="93"/>
       <c r="Z25" s="117"/>
       <c r="AA25" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB25" s="93"/>
       <c r="AC25" s="93"/>
       <c r="AD25" s="93"/>
       <c r="AE25" s="94"/>
       <c r="AF25" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG25" s="99"/>
       <c r="AH25" s="100"/>
       <c r="AI25" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ25" s="99"/>
       <c r="AK25" s="105"/>
@@ -8011,41 +8004,41 @@
       <c r="BC25" s="87"/>
       <c r="BD25" s="88"/>
       <c r="BE25" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF25" s="65"/>
       <c r="BG25" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH25" s="68"/>
       <c r="BI25" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ25" s="71"/>
       <c r="BK25" s="71"/>
       <c r="BL25" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM25" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN25" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN25" s="23" t="s">
+      <c r="BO25" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO25" s="23" t="s">
+      <c r="BP25" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP25" s="23" t="s">
+      <c r="BQ25" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ25" s="23" t="s">
+      <c r="BR25" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR25" s="23" t="s">
+      <c r="BS25" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS25" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT25" s="71"/>
       <c r="BU25" s="71"/>
@@ -8131,7 +8124,7 @@
       <c r="BG26" s="120"/>
       <c r="BH26" s="121"/>
       <c r="BI26" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ26" s="120"/>
       <c r="BK26" s="120"/>
@@ -8167,12 +8160,12 @@
     </row>
     <row r="27" spans="1:92" ht="15" customHeight="1">
       <c r="A27" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B27" s="71"/>
       <c r="C27" s="112"/>
       <c r="D27" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E27" s="71"/>
       <c r="F27" s="72"/>
@@ -8183,12 +8176,12 @@
       <c r="K27" s="31"/>
       <c r="L27" s="31"/>
       <c r="M27" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N27" s="71"/>
       <c r="O27" s="31"/>
       <c r="P27" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="71"/>
       <c r="R27" s="29"/>
@@ -8196,26 +8189,26 @@
       <c r="T27" s="115"/>
       <c r="U27" s="112"/>
       <c r="V27" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W27" s="93"/>
       <c r="X27" s="93"/>
       <c r="Y27" s="93"/>
       <c r="Z27" s="117"/>
       <c r="AA27" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB27" s="93"/>
       <c r="AC27" s="93"/>
       <c r="AD27" s="93"/>
       <c r="AE27" s="94"/>
       <c r="AF27" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG27" s="99"/>
       <c r="AH27" s="100"/>
       <c r="AI27" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ27" s="99"/>
       <c r="AK27" s="105"/>
@@ -8239,41 +8232,41 @@
       <c r="BC27" s="87"/>
       <c r="BD27" s="88"/>
       <c r="BE27" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF27" s="65"/>
       <c r="BG27" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH27" s="68"/>
       <c r="BI27" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ27" s="71"/>
       <c r="BK27" s="71"/>
       <c r="BL27" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM27" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN27" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN27" s="23" t="s">
+      <c r="BO27" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO27" s="23" t="s">
+      <c r="BP27" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP27" s="23" t="s">
+      <c r="BQ27" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ27" s="23" t="s">
+      <c r="BR27" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR27" s="23" t="s">
+      <c r="BS27" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS27" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT27" s="71"/>
       <c r="BU27" s="71"/>
@@ -8359,7 +8352,7 @@
       <c r="BG28" s="120"/>
       <c r="BH28" s="121"/>
       <c r="BI28" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ28" s="120"/>
       <c r="BK28" s="120"/>
@@ -8395,12 +8388,12 @@
     </row>
     <row r="29" spans="1:92" ht="15" customHeight="1">
       <c r="A29" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" s="71"/>
       <c r="C29" s="112"/>
       <c r="D29" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E29" s="71"/>
       <c r="F29" s="72"/>
@@ -8411,12 +8404,12 @@
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N29" s="71"/>
       <c r="O29" s="31"/>
       <c r="P29" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q29" s="71"/>
       <c r="R29" s="29"/>
@@ -8424,26 +8417,26 @@
       <c r="T29" s="115"/>
       <c r="U29" s="112"/>
       <c r="V29" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W29" s="93"/>
       <c r="X29" s="93"/>
       <c r="Y29" s="93"/>
       <c r="Z29" s="117"/>
       <c r="AA29" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB29" s="93"/>
       <c r="AC29" s="93"/>
       <c r="AD29" s="93"/>
       <c r="AE29" s="94"/>
       <c r="AF29" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG29" s="99"/>
       <c r="AH29" s="100"/>
       <c r="AI29" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ29" s="99"/>
       <c r="AK29" s="105"/>
@@ -8467,41 +8460,41 @@
       <c r="BC29" s="87"/>
       <c r="BD29" s="88"/>
       <c r="BE29" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF29" s="65"/>
       <c r="BG29" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH29" s="68"/>
       <c r="BI29" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ29" s="71"/>
       <c r="BK29" s="71"/>
       <c r="BL29" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM29" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN29" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN29" s="23" t="s">
+      <c r="BO29" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO29" s="23" t="s">
+      <c r="BP29" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP29" s="23" t="s">
+      <c r="BQ29" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ29" s="23" t="s">
+      <c r="BR29" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR29" s="23" t="s">
+      <c r="BS29" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS29" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT29" s="71"/>
       <c r="BU29" s="71"/>
@@ -8587,7 +8580,7 @@
       <c r="BG30" s="120"/>
       <c r="BH30" s="121"/>
       <c r="BI30" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ30" s="120"/>
       <c r="BK30" s="120"/>
@@ -8623,12 +8616,12 @@
     </row>
     <row r="31" spans="1:92" ht="15" customHeight="1">
       <c r="A31" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" s="71"/>
       <c r="C31" s="112"/>
       <c r="D31" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E31" s="71"/>
       <c r="F31" s="72"/>
@@ -8639,12 +8632,12 @@
       <c r="K31" s="31"/>
       <c r="L31" s="31"/>
       <c r="M31" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N31" s="71"/>
       <c r="O31" s="31"/>
       <c r="P31" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q31" s="71"/>
       <c r="R31" s="29"/>
@@ -8652,26 +8645,26 @@
       <c r="T31" s="115"/>
       <c r="U31" s="112"/>
       <c r="V31" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W31" s="93"/>
       <c r="X31" s="93"/>
       <c r="Y31" s="93"/>
       <c r="Z31" s="117"/>
       <c r="AA31" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB31" s="93"/>
       <c r="AC31" s="93"/>
       <c r="AD31" s="93"/>
       <c r="AE31" s="94"/>
       <c r="AF31" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG31" s="99"/>
       <c r="AH31" s="100"/>
       <c r="AI31" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ31" s="99"/>
       <c r="AK31" s="105"/>
@@ -8695,41 +8688,41 @@
       <c r="BC31" s="87"/>
       <c r="BD31" s="88"/>
       <c r="BE31" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF31" s="65"/>
       <c r="BG31" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH31" s="68"/>
       <c r="BI31" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ31" s="71"/>
       <c r="BK31" s="71"/>
       <c r="BL31" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM31" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN31" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN31" s="23" t="s">
+      <c r="BO31" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO31" s="23" t="s">
+      <c r="BP31" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP31" s="23" t="s">
+      <c r="BQ31" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ31" s="23" t="s">
+      <c r="BR31" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR31" s="23" t="s">
+      <c r="BS31" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS31" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT31" s="71"/>
       <c r="BU31" s="71"/>
@@ -8815,7 +8808,7 @@
       <c r="BG32" s="120"/>
       <c r="BH32" s="121"/>
       <c r="BI32" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ32" s="120"/>
       <c r="BK32" s="120"/>
@@ -8851,12 +8844,12 @@
     </row>
     <row r="33" spans="1:92" ht="15" customHeight="1">
       <c r="A33" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" s="71"/>
       <c r="C33" s="112"/>
       <c r="D33" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E33" s="71"/>
       <c r="F33" s="72"/>
@@ -8867,12 +8860,12 @@
       <c r="K33" s="31"/>
       <c r="L33" s="31"/>
       <c r="M33" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N33" s="71"/>
       <c r="O33" s="31"/>
       <c r="P33" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q33" s="71"/>
       <c r="R33" s="29"/>
@@ -8880,26 +8873,26 @@
       <c r="T33" s="115"/>
       <c r="U33" s="112"/>
       <c r="V33" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W33" s="93"/>
       <c r="X33" s="93"/>
       <c r="Y33" s="93"/>
       <c r="Z33" s="117"/>
       <c r="AA33" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB33" s="93"/>
       <c r="AC33" s="93"/>
       <c r="AD33" s="93"/>
       <c r="AE33" s="94"/>
       <c r="AF33" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG33" s="99"/>
       <c r="AH33" s="100"/>
       <c r="AI33" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ33" s="99"/>
       <c r="AK33" s="105"/>
@@ -8923,41 +8916,41 @@
       <c r="BC33" s="87"/>
       <c r="BD33" s="88"/>
       <c r="BE33" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF33" s="65"/>
       <c r="BG33" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH33" s="68"/>
       <c r="BI33" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ33" s="71"/>
       <c r="BK33" s="71"/>
       <c r="BL33" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM33" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN33" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN33" s="23" t="s">
+      <c r="BO33" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO33" s="23" t="s">
+      <c r="BP33" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP33" s="23" t="s">
+      <c r="BQ33" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ33" s="23" t="s">
+      <c r="BR33" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR33" s="23" t="s">
+      <c r="BS33" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS33" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT33" s="71"/>
       <c r="BU33" s="71"/>
@@ -9043,7 +9036,7 @@
       <c r="BG34" s="120"/>
       <c r="BH34" s="121"/>
       <c r="BI34" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ34" s="120"/>
       <c r="BK34" s="120"/>
@@ -9079,12 +9072,12 @@
     </row>
     <row r="35" spans="1:92" ht="15" customHeight="1">
       <c r="A35" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" s="71"/>
       <c r="C35" s="112"/>
       <c r="D35" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E35" s="71"/>
       <c r="F35" s="72"/>
@@ -9095,12 +9088,12 @@
       <c r="K35" s="31"/>
       <c r="L35" s="31"/>
       <c r="M35" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N35" s="71"/>
       <c r="O35" s="31"/>
       <c r="P35" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q35" s="71"/>
       <c r="R35" s="29"/>
@@ -9108,26 +9101,26 @@
       <c r="T35" s="115"/>
       <c r="U35" s="112"/>
       <c r="V35" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W35" s="93"/>
       <c r="X35" s="93"/>
       <c r="Y35" s="93"/>
       <c r="Z35" s="117"/>
       <c r="AA35" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB35" s="93"/>
       <c r="AC35" s="93"/>
       <c r="AD35" s="93"/>
       <c r="AE35" s="94"/>
       <c r="AF35" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG35" s="99"/>
       <c r="AH35" s="100"/>
       <c r="AI35" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ35" s="99"/>
       <c r="AK35" s="105"/>
@@ -9151,41 +9144,41 @@
       <c r="BC35" s="87"/>
       <c r="BD35" s="88"/>
       <c r="BE35" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF35" s="65"/>
       <c r="BG35" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH35" s="68"/>
       <c r="BI35" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ35" s="71"/>
       <c r="BK35" s="71"/>
       <c r="BL35" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM35" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN35" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN35" s="23" t="s">
+      <c r="BO35" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO35" s="23" t="s">
+      <c r="BP35" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP35" s="23" t="s">
+      <c r="BQ35" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ35" s="23" t="s">
+      <c r="BR35" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR35" s="23" t="s">
+      <c r="BS35" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS35" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT35" s="71"/>
       <c r="BU35" s="71"/>
@@ -9271,7 +9264,7 @@
       <c r="BG36" s="120"/>
       <c r="BH36" s="121"/>
       <c r="BI36" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ36" s="120"/>
       <c r="BK36" s="120"/>
@@ -9307,12 +9300,12 @@
     </row>
     <row r="37" spans="1:92" ht="15" customHeight="1">
       <c r="A37" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" s="71"/>
       <c r="C37" s="112"/>
       <c r="D37" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E37" s="71"/>
       <c r="F37" s="72"/>
@@ -9323,12 +9316,12 @@
       <c r="K37" s="31"/>
       <c r="L37" s="31"/>
       <c r="M37" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N37" s="71"/>
       <c r="O37" s="31"/>
       <c r="P37" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q37" s="71"/>
       <c r="R37" s="29"/>
@@ -9336,26 +9329,26 @@
       <c r="T37" s="115"/>
       <c r="U37" s="112"/>
       <c r="V37" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W37" s="93"/>
       <c r="X37" s="93"/>
       <c r="Y37" s="93"/>
       <c r="Z37" s="117"/>
       <c r="AA37" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB37" s="93"/>
       <c r="AC37" s="93"/>
       <c r="AD37" s="93"/>
       <c r="AE37" s="94"/>
       <c r="AF37" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG37" s="99"/>
       <c r="AH37" s="100"/>
       <c r="AI37" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ37" s="99"/>
       <c r="AK37" s="105"/>
@@ -9379,41 +9372,41 @@
       <c r="BC37" s="87"/>
       <c r="BD37" s="88"/>
       <c r="BE37" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF37" s="65"/>
       <c r="BG37" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH37" s="68"/>
       <c r="BI37" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ37" s="71"/>
       <c r="BK37" s="71"/>
       <c r="BL37" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM37" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN37" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN37" s="23" t="s">
+      <c r="BO37" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO37" s="23" t="s">
+      <c r="BP37" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP37" s="23" t="s">
+      <c r="BQ37" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ37" s="23" t="s">
+      <c r="BR37" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR37" s="23" t="s">
+      <c r="BS37" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS37" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT37" s="71"/>
       <c r="BU37" s="71"/>
@@ -9499,7 +9492,7 @@
       <c r="BG38" s="120"/>
       <c r="BH38" s="121"/>
       <c r="BI38" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ38" s="120"/>
       <c r="BK38" s="120"/>
@@ -9535,12 +9528,12 @@
     </row>
     <row r="39" spans="1:92" ht="15" customHeight="1">
       <c r="A39" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" s="71"/>
       <c r="C39" s="112"/>
       <c r="D39" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E39" s="71"/>
       <c r="F39" s="72"/>
@@ -9551,12 +9544,12 @@
       <c r="K39" s="31"/>
       <c r="L39" s="31"/>
       <c r="M39" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N39" s="71"/>
       <c r="O39" s="31"/>
       <c r="P39" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q39" s="71"/>
       <c r="R39" s="29"/>
@@ -9564,26 +9557,26 @@
       <c r="T39" s="115"/>
       <c r="U39" s="112"/>
       <c r="V39" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W39" s="93"/>
       <c r="X39" s="93"/>
       <c r="Y39" s="93"/>
       <c r="Z39" s="117"/>
       <c r="AA39" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB39" s="93"/>
       <c r="AC39" s="93"/>
       <c r="AD39" s="93"/>
       <c r="AE39" s="94"/>
       <c r="AF39" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG39" s="99"/>
       <c r="AH39" s="100"/>
       <c r="AI39" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ39" s="99"/>
       <c r="AK39" s="105"/>
@@ -9607,41 +9600,41 @@
       <c r="BC39" s="87"/>
       <c r="BD39" s="88"/>
       <c r="BE39" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF39" s="65"/>
       <c r="BG39" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH39" s="68"/>
       <c r="BI39" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ39" s="71"/>
       <c r="BK39" s="71"/>
       <c r="BL39" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM39" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN39" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN39" s="23" t="s">
+      <c r="BO39" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO39" s="23" t="s">
+      <c r="BP39" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP39" s="23" t="s">
+      <c r="BQ39" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ39" s="23" t="s">
+      <c r="BR39" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR39" s="23" t="s">
+      <c r="BS39" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS39" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT39" s="71"/>
       <c r="BU39" s="71"/>
@@ -9727,7 +9720,7 @@
       <c r="BG40" s="120"/>
       <c r="BH40" s="121"/>
       <c r="BI40" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ40" s="120"/>
       <c r="BK40" s="120"/>
@@ -9763,12 +9756,12 @@
     </row>
     <row r="41" spans="1:92" ht="15" customHeight="1">
       <c r="A41" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B41" s="71"/>
       <c r="C41" s="112"/>
       <c r="D41" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E41" s="71"/>
       <c r="F41" s="72"/>
@@ -9779,12 +9772,12 @@
       <c r="K41" s="31"/>
       <c r="L41" s="31"/>
       <c r="M41" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N41" s="71"/>
       <c r="O41" s="31"/>
       <c r="P41" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q41" s="71"/>
       <c r="R41" s="29"/>
@@ -9792,26 +9785,26 @@
       <c r="T41" s="115"/>
       <c r="U41" s="112"/>
       <c r="V41" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W41" s="93"/>
       <c r="X41" s="93"/>
       <c r="Y41" s="93"/>
       <c r="Z41" s="117"/>
       <c r="AA41" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB41" s="93"/>
       <c r="AC41" s="93"/>
       <c r="AD41" s="93"/>
       <c r="AE41" s="94"/>
       <c r="AF41" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG41" s="99"/>
       <c r="AH41" s="100"/>
       <c r="AI41" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ41" s="99"/>
       <c r="AK41" s="105"/>
@@ -9835,41 +9828,41 @@
       <c r="BC41" s="87"/>
       <c r="BD41" s="88"/>
       <c r="BE41" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF41" s="65"/>
       <c r="BG41" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH41" s="68"/>
       <c r="BI41" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ41" s="71"/>
       <c r="BK41" s="71"/>
       <c r="BL41" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM41" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN41" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN41" s="23" t="s">
+      <c r="BO41" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO41" s="23" t="s">
+      <c r="BP41" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP41" s="23" t="s">
+      <c r="BQ41" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ41" s="23" t="s">
+      <c r="BR41" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR41" s="23" t="s">
+      <c r="BS41" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS41" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT41" s="71"/>
       <c r="BU41" s="71"/>
@@ -9955,7 +9948,7 @@
       <c r="BG42" s="120"/>
       <c r="BH42" s="121"/>
       <c r="BI42" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ42" s="120"/>
       <c r="BK42" s="120"/>
@@ -9991,12 +9984,12 @@
     </row>
     <row r="43" spans="1:92" ht="15" customHeight="1">
       <c r="A43" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" s="71"/>
       <c r="C43" s="112"/>
       <c r="D43" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E43" s="71"/>
       <c r="F43" s="72"/>
@@ -10007,12 +10000,12 @@
       <c r="K43" s="31"/>
       <c r="L43" s="31"/>
       <c r="M43" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N43" s="71"/>
       <c r="O43" s="31"/>
       <c r="P43" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q43" s="71"/>
       <c r="R43" s="29"/>
@@ -10020,26 +10013,26 @@
       <c r="T43" s="115"/>
       <c r="U43" s="112"/>
       <c r="V43" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W43" s="93"/>
       <c r="X43" s="93"/>
       <c r="Y43" s="93"/>
       <c r="Z43" s="117"/>
       <c r="AA43" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB43" s="93"/>
       <c r="AC43" s="93"/>
       <c r="AD43" s="93"/>
       <c r="AE43" s="94"/>
       <c r="AF43" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG43" s="99"/>
       <c r="AH43" s="100"/>
       <c r="AI43" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ43" s="99"/>
       <c r="AK43" s="105"/>
@@ -10063,41 +10056,41 @@
       <c r="BC43" s="87"/>
       <c r="BD43" s="88"/>
       <c r="BE43" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF43" s="65"/>
       <c r="BG43" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH43" s="68"/>
       <c r="BI43" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ43" s="71"/>
       <c r="BK43" s="71"/>
       <c r="BL43" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM43" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN43" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN43" s="23" t="s">
+      <c r="BO43" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO43" s="23" t="s">
+      <c r="BP43" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP43" s="23" t="s">
+      <c r="BQ43" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ43" s="23" t="s">
+      <c r="BR43" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR43" s="23" t="s">
+      <c r="BS43" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS43" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT43" s="71"/>
       <c r="BU43" s="71"/>
@@ -10183,7 +10176,7 @@
       <c r="BG44" s="120"/>
       <c r="BH44" s="121"/>
       <c r="BI44" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ44" s="120"/>
       <c r="BK44" s="120"/>
@@ -10219,12 +10212,12 @@
     </row>
     <row r="45" spans="1:92" ht="15" customHeight="1">
       <c r="A45" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B45" s="71"/>
       <c r="C45" s="112"/>
       <c r="D45" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E45" s="71"/>
       <c r="F45" s="72"/>
@@ -10235,12 +10228,12 @@
       <c r="K45" s="31"/>
       <c r="L45" s="31"/>
       <c r="M45" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N45" s="71"/>
       <c r="O45" s="31"/>
       <c r="P45" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q45" s="71"/>
       <c r="R45" s="29"/>
@@ -10248,26 +10241,26 @@
       <c r="T45" s="115"/>
       <c r="U45" s="112"/>
       <c r="V45" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W45" s="93"/>
       <c r="X45" s="93"/>
       <c r="Y45" s="93"/>
       <c r="Z45" s="117"/>
       <c r="AA45" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB45" s="93"/>
       <c r="AC45" s="93"/>
       <c r="AD45" s="93"/>
       <c r="AE45" s="94"/>
       <c r="AF45" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG45" s="99"/>
       <c r="AH45" s="100"/>
       <c r="AI45" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ45" s="99"/>
       <c r="AK45" s="105"/>
@@ -10291,41 +10284,41 @@
       <c r="BC45" s="87"/>
       <c r="BD45" s="88"/>
       <c r="BE45" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF45" s="65"/>
       <c r="BG45" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH45" s="68"/>
       <c r="BI45" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ45" s="71"/>
       <c r="BK45" s="71"/>
       <c r="BL45" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM45" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN45" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN45" s="23" t="s">
+      <c r="BO45" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO45" s="23" t="s">
+      <c r="BP45" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP45" s="23" t="s">
+      <c r="BQ45" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ45" s="23" t="s">
+      <c r="BR45" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR45" s="23" t="s">
+      <c r="BS45" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS45" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT45" s="71"/>
       <c r="BU45" s="71"/>
@@ -10411,7 +10404,7 @@
       <c r="BG46" s="120"/>
       <c r="BH46" s="121"/>
       <c r="BI46" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ46" s="120"/>
       <c r="BK46" s="120"/>
@@ -10447,12 +10440,12 @@
     </row>
     <row r="47" spans="1:92" ht="15" customHeight="1">
       <c r="A47" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B47" s="71"/>
       <c r="C47" s="112"/>
       <c r="D47" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E47" s="71"/>
       <c r="F47" s="72"/>
@@ -10463,12 +10456,12 @@
       <c r="K47" s="31"/>
       <c r="L47" s="31"/>
       <c r="M47" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N47" s="71"/>
       <c r="O47" s="31"/>
       <c r="P47" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q47" s="71"/>
       <c r="R47" s="29"/>
@@ -10476,26 +10469,26 @@
       <c r="T47" s="115"/>
       <c r="U47" s="112"/>
       <c r="V47" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W47" s="93"/>
       <c r="X47" s="93"/>
       <c r="Y47" s="93"/>
       <c r="Z47" s="117"/>
       <c r="AA47" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB47" s="93"/>
       <c r="AC47" s="93"/>
       <c r="AD47" s="93"/>
       <c r="AE47" s="94"/>
       <c r="AF47" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG47" s="99"/>
       <c r="AH47" s="100"/>
       <c r="AI47" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ47" s="99"/>
       <c r="AK47" s="105"/>
@@ -10519,41 +10512,41 @@
       <c r="BC47" s="87"/>
       <c r="BD47" s="88"/>
       <c r="BE47" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF47" s="65"/>
       <c r="BG47" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH47" s="68"/>
       <c r="BI47" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ47" s="71"/>
       <c r="BK47" s="71"/>
       <c r="BL47" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM47" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN47" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN47" s="23" t="s">
+      <c r="BO47" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO47" s="23" t="s">
+      <c r="BP47" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP47" s="23" t="s">
+      <c r="BQ47" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ47" s="23" t="s">
+      <c r="BR47" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR47" s="23" t="s">
+      <c r="BS47" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS47" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT47" s="71"/>
       <c r="BU47" s="71"/>
@@ -10639,7 +10632,7 @@
       <c r="BG48" s="120"/>
       <c r="BH48" s="121"/>
       <c r="BI48" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ48" s="120"/>
       <c r="BK48" s="120"/>
@@ -10675,12 +10668,12 @@
     </row>
     <row r="49" spans="1:92" ht="15" customHeight="1">
       <c r="A49" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" s="71"/>
       <c r="C49" s="112"/>
       <c r="D49" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E49" s="71"/>
       <c r="F49" s="72"/>
@@ -10691,12 +10684,12 @@
       <c r="K49" s="31"/>
       <c r="L49" s="31"/>
       <c r="M49" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N49" s="71"/>
       <c r="O49" s="31"/>
       <c r="P49" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q49" s="71"/>
       <c r="R49" s="29"/>
@@ -10704,26 +10697,26 @@
       <c r="T49" s="115"/>
       <c r="U49" s="112"/>
       <c r="V49" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W49" s="93"/>
       <c r="X49" s="93"/>
       <c r="Y49" s="93"/>
       <c r="Z49" s="117"/>
       <c r="AA49" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB49" s="93"/>
       <c r="AC49" s="93"/>
       <c r="AD49" s="93"/>
       <c r="AE49" s="94"/>
       <c r="AF49" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG49" s="99"/>
       <c r="AH49" s="100"/>
       <c r="AI49" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ49" s="99"/>
       <c r="AK49" s="105"/>
@@ -10747,41 +10740,41 @@
       <c r="BC49" s="87"/>
       <c r="BD49" s="88"/>
       <c r="BE49" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF49" s="65"/>
       <c r="BG49" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH49" s="68"/>
       <c r="BI49" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ49" s="71"/>
       <c r="BK49" s="71"/>
       <c r="BL49" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM49" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN49" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN49" s="23" t="s">
+      <c r="BO49" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO49" s="23" t="s">
+      <c r="BP49" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP49" s="23" t="s">
+      <c r="BQ49" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ49" s="23" t="s">
+      <c r="BR49" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR49" s="23" t="s">
+      <c r="BS49" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS49" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT49" s="71"/>
       <c r="BU49" s="71"/>
@@ -10867,7 +10860,7 @@
       <c r="BG50" s="120"/>
       <c r="BH50" s="121"/>
       <c r="BI50" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ50" s="120"/>
       <c r="BK50" s="120"/>
@@ -10903,12 +10896,12 @@
     </row>
     <row r="51" spans="1:92" ht="15" customHeight="1">
       <c r="A51" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51" s="71"/>
       <c r="C51" s="112"/>
       <c r="D51" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E51" s="71"/>
       <c r="F51" s="72"/>
@@ -10919,12 +10912,12 @@
       <c r="K51" s="31"/>
       <c r="L51" s="31"/>
       <c r="M51" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N51" s="71"/>
       <c r="O51" s="31"/>
       <c r="P51" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q51" s="71"/>
       <c r="R51" s="29"/>
@@ -10932,26 +10925,26 @@
       <c r="T51" s="115"/>
       <c r="U51" s="112"/>
       <c r="V51" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W51" s="93"/>
       <c r="X51" s="93"/>
       <c r="Y51" s="93"/>
       <c r="Z51" s="117"/>
       <c r="AA51" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB51" s="93"/>
       <c r="AC51" s="93"/>
       <c r="AD51" s="93"/>
       <c r="AE51" s="94"/>
       <c r="AF51" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG51" s="99"/>
       <c r="AH51" s="100"/>
       <c r="AI51" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ51" s="99"/>
       <c r="AK51" s="105"/>
@@ -10975,41 +10968,41 @@
       <c r="BC51" s="87"/>
       <c r="BD51" s="88"/>
       <c r="BE51" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF51" s="65"/>
       <c r="BG51" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH51" s="68"/>
       <c r="BI51" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ51" s="71"/>
       <c r="BK51" s="71"/>
       <c r="BL51" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM51" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN51" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN51" s="23" t="s">
+      <c r="BO51" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO51" s="23" t="s">
+      <c r="BP51" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP51" s="23" t="s">
+      <c r="BQ51" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ51" s="23" t="s">
+      <c r="BR51" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR51" s="23" t="s">
+      <c r="BS51" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS51" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT51" s="71"/>
       <c r="BU51" s="71"/>
@@ -11095,7 +11088,7 @@
       <c r="BG52" s="120"/>
       <c r="BH52" s="121"/>
       <c r="BI52" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ52" s="120"/>
       <c r="BK52" s="120"/>
@@ -11131,12 +11124,12 @@
     </row>
     <row r="53" spans="1:92" ht="15" customHeight="1">
       <c r="A53" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B53" s="71"/>
       <c r="C53" s="112"/>
       <c r="D53" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E53" s="71"/>
       <c r="F53" s="72"/>
@@ -11147,12 +11140,12 @@
       <c r="K53" s="31"/>
       <c r="L53" s="31"/>
       <c r="M53" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N53" s="71"/>
       <c r="O53" s="31"/>
       <c r="P53" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q53" s="71"/>
       <c r="R53" s="29"/>
@@ -11160,26 +11153,26 @@
       <c r="T53" s="115"/>
       <c r="U53" s="112"/>
       <c r="V53" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W53" s="93"/>
       <c r="X53" s="93"/>
       <c r="Y53" s="93"/>
       <c r="Z53" s="117"/>
       <c r="AA53" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB53" s="93"/>
       <c r="AC53" s="93"/>
       <c r="AD53" s="93"/>
       <c r="AE53" s="94"/>
       <c r="AF53" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG53" s="99"/>
       <c r="AH53" s="100"/>
       <c r="AI53" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ53" s="99"/>
       <c r="AK53" s="105"/>
@@ -11203,41 +11196,41 @@
       <c r="BC53" s="87"/>
       <c r="BD53" s="88"/>
       <c r="BE53" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF53" s="65"/>
       <c r="BG53" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH53" s="68"/>
       <c r="BI53" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ53" s="71"/>
       <c r="BK53" s="71"/>
       <c r="BL53" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM53" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN53" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN53" s="23" t="s">
+      <c r="BO53" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO53" s="23" t="s">
+      <c r="BP53" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP53" s="23" t="s">
+      <c r="BQ53" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ53" s="23" t="s">
+      <c r="BR53" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR53" s="23" t="s">
+      <c r="BS53" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS53" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT53" s="71"/>
       <c r="BU53" s="71"/>
@@ -11323,7 +11316,7 @@
       <c r="BG54" s="120"/>
       <c r="BH54" s="121"/>
       <c r="BI54" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ54" s="120"/>
       <c r="BK54" s="120"/>
@@ -11359,12 +11352,12 @@
     </row>
     <row r="55" spans="1:92" ht="15" customHeight="1">
       <c r="A55" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B55" s="71"/>
       <c r="C55" s="112"/>
       <c r="D55" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E55" s="71"/>
       <c r="F55" s="72"/>
@@ -11375,12 +11368,12 @@
       <c r="K55" s="31"/>
       <c r="L55" s="31"/>
       <c r="M55" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N55" s="71"/>
       <c r="O55" s="31"/>
       <c r="P55" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q55" s="71"/>
       <c r="R55" s="29"/>
@@ -11388,26 +11381,26 @@
       <c r="T55" s="115"/>
       <c r="U55" s="112"/>
       <c r="V55" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W55" s="93"/>
       <c r="X55" s="93"/>
       <c r="Y55" s="93"/>
       <c r="Z55" s="117"/>
       <c r="AA55" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB55" s="93"/>
       <c r="AC55" s="93"/>
       <c r="AD55" s="93"/>
       <c r="AE55" s="94"/>
       <c r="AF55" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG55" s="99"/>
       <c r="AH55" s="100"/>
       <c r="AI55" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ55" s="99"/>
       <c r="AK55" s="105"/>
@@ -11431,41 +11424,41 @@
       <c r="BC55" s="87"/>
       <c r="BD55" s="88"/>
       <c r="BE55" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF55" s="65"/>
       <c r="BG55" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH55" s="68"/>
       <c r="BI55" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ55" s="71"/>
       <c r="BK55" s="71"/>
       <c r="BL55" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM55" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN55" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN55" s="23" t="s">
+      <c r="BO55" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO55" s="23" t="s">
+      <c r="BP55" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP55" s="23" t="s">
+      <c r="BQ55" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ55" s="23" t="s">
+      <c r="BR55" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR55" s="23" t="s">
+      <c r="BS55" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS55" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT55" s="71"/>
       <c r="BU55" s="71"/>
@@ -11551,7 +11544,7 @@
       <c r="BG56" s="120"/>
       <c r="BH56" s="121"/>
       <c r="BI56" s="122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ56" s="120"/>
       <c r="BK56" s="120"/>
@@ -11587,12 +11580,12 @@
     </row>
     <row r="57" spans="1:92" ht="15" customHeight="1">
       <c r="A57" s="111" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B57" s="71"/>
       <c r="C57" s="112"/>
       <c r="D57" s="115" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57" s="71"/>
       <c r="F57" s="72"/>
@@ -11601,11 +11594,11 @@
       <c r="I57" s="6"/>
       <c r="J57" s="9"/>
       <c r="M57" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N57" s="71"/>
       <c r="P57" s="71" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q57" s="71"/>
       <c r="R57" s="6"/>
@@ -11613,26 +11606,26 @@
       <c r="T57" s="115"/>
       <c r="U57" s="112"/>
       <c r="V57" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="W57" s="93"/>
       <c r="X57" s="93"/>
       <c r="Y57" s="93"/>
       <c r="Z57" s="117"/>
       <c r="AA57" s="92" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB57" s="93"/>
       <c r="AC57" s="93"/>
       <c r="AD57" s="93"/>
       <c r="AE57" s="94"/>
       <c r="AF57" s="98" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG57" s="99"/>
       <c r="AH57" s="100"/>
       <c r="AI57" s="104" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AJ57" s="99"/>
       <c r="AK57" s="105"/>
@@ -11656,41 +11649,41 @@
       <c r="BC57" s="87"/>
       <c r="BD57" s="88"/>
       <c r="BE57" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BF57" s="65"/>
       <c r="BG57" s="65" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BH57" s="68"/>
       <c r="BI57" s="70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BJ57" s="71"/>
       <c r="BK57" s="71"/>
       <c r="BL57" s="22" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="BM57" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="BN57" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="BN57" s="23" t="s">
+      <c r="BO57" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="BO57" s="23" t="s">
+      <c r="BP57" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="BP57" s="23" t="s">
+      <c r="BQ57" s="23" t="s">
         <v>116</v>
       </c>
-      <c r="BQ57" s="23" t="s">
+      <c r="BR57" s="23" t="s">
         <v>117</v>
       </c>
-      <c r="BR57" s="23" t="s">
+      <c r="BS57" s="24" t="s">
         <v>118</v>
-      </c>
-      <c r="BS57" s="24" t="s">
-        <v>119</v>
       </c>
       <c r="BT57" s="71"/>
       <c r="BU57" s="71"/>
@@ -11776,7 +11769,7 @@
       <c r="BG58" s="67"/>
       <c r="BH58" s="69"/>
       <c r="BI58" s="77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="BJ58" s="67"/>
       <c r="BK58" s="67"/>
